--- a/nifty100_capstone/data/raw/sectors.xlsx
+++ b/nifty100_capstone/data/raw/sectors.xlsx
@@ -14,42 +14,468 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>sector_id</t>
-  </si>
-  <si>
-    <t>sector_name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="154">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>company_id</t>
+  </si>
+  <si>
+    <t>broad_sector</t>
+  </si>
+  <si>
+    <t>sub_sector</t>
+  </si>
+  <si>
+    <t>index_weight_pct</t>
+  </si>
+  <si>
+    <t>market_cap_category</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>ADANIENSOL</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>ADANIGREEN</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>ADANIPOWER</t>
+  </si>
+  <si>
+    <t>AMBUJACEM</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>ATGL</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BAJAJHLDNG</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>BANKBARODA</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>BHEL</t>
+  </si>
+  <si>
+    <t>BOSCHLTD</t>
+  </si>
+  <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>BRITANNIA</t>
+  </si>
+  <si>
+    <t>CANBK</t>
+  </si>
+  <si>
+    <t>CHOLAFIN</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>DABUR</t>
+  </si>
+  <si>
+    <t>DIVISLAB</t>
+  </si>
+  <si>
+    <t>DLF</t>
+  </si>
+  <si>
+    <t>DMART</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>GAIL</t>
+  </si>
+  <si>
+    <t>GODREJCP</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>HAVELLS</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>HEROMOTOCO</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>ICICIGI</t>
+  </si>
+  <si>
+    <t>ICICIPRULI</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>INDUSINDBK</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>IOC</t>
+  </si>
+  <si>
+    <t>IRCTC</t>
+  </si>
+  <si>
+    <t>IRFC</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>JINDALSTEL</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>JSWENERGY</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>LICI</t>
+  </si>
+  <si>
+    <t>LODHA</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>LTIM</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>MOTHERSON</t>
+  </si>
+  <si>
+    <t>NAUKRI</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>NHPC</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>PIDILITIND</t>
+  </si>
+  <si>
+    <t>PNB</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>RECLTD</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>SHREECEM</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>TATAMOTORS</t>
+  </si>
+  <si>
+    <t>TATAPOWER</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>TORNTPHARM</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>TVSMOTOR</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
   </si>
   <si>
     <t>Information Technology</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Healthcare &amp; Pharma</t>
-  </si>
-  <si>
-    <t>Automobile</t>
-  </si>
-  <si>
-    <t>Energy &amp; Power</t>
-  </si>
-  <si>
-    <t>Fast Moving Consumer Goods</t>
+    <t>Capital Goods</t>
+  </si>
+  <si>
+    <t>Power &amp; Utilities</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Paints &amp; Coatings</t>
+  </si>
+  <si>
+    <t>Gas Distribution</t>
+  </si>
+  <si>
+    <t>Private Banks</t>
+  </si>
+  <si>
+    <t>Two Wheelers</t>
+  </si>
+  <si>
+    <t>Diversified Financials</t>
+  </si>
+  <si>
+    <t>Holding Companies</t>
+  </si>
+  <si>
+    <t>Consumer Finance</t>
+  </si>
+  <si>
+    <t>Public Sector Banks</t>
+  </si>
+  <si>
+    <t>Defence Electronics</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>Auto Ancillaries</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Mining &amp; Metals</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Diversified Industrials</t>
+  </si>
+  <si>
+    <t>Defence &amp; Aerospace</t>
+  </si>
+  <si>
+    <t>Consumer Electricals</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
   </si>
   <si>
     <t>Metals &amp; Mining</t>
   </si>
   <si>
-    <t>Telecommunication</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
+    <t>FMCG</t>
+  </si>
+  <si>
+    <t>General Insurance</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Travel &amp; Tourism</t>
+  </si>
+  <si>
+    <t>Speciality Finance</t>
+  </si>
+  <si>
+    <t>Diversified FMCG</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Internet &amp; Platforms</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Exploration</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>Power Transmission</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverages</t>
+  </si>
+  <si>
+    <t>Gems &amp; Jewellery</t>
+  </si>
+  <si>
+    <t>Large Cap</t>
+  </si>
+  <si>
+    <t>Mid Cap</t>
   </si>
 </sst>
 </file>
@@ -381,95 +807,1867 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3">
+        <v>0.65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4">
+        <v>1.5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5">
+        <v>1.23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6">
+        <v>2.12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7">
+        <v>3.01</v>
+      </c>
+      <c r="F7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8">
+        <v>2.82</v>
+      </c>
+      <c r="F8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9">
+        <v>0.62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10">
+        <v>1.13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12">
+        <v>2.97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13">
+        <v>3.9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14">
+        <v>2.12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15">
+        <v>3.36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16">
+        <v>1.78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17">
+        <v>1.27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18">
+        <v>3.65</v>
+      </c>
+      <c r="F18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19">
+        <v>1.13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20">
+        <v>1.24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21">
+        <v>2.82</v>
+      </c>
+      <c r="F21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22">
+        <v>2.57</v>
+      </c>
+      <c r="F22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23">
+        <v>0.66</v>
+      </c>
+      <c r="F23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24">
+        <v>2.96</v>
+      </c>
+      <c r="F24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25">
+        <v>3.94</v>
+      </c>
+      <c r="F25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26">
+        <v>0.95</v>
+      </c>
+      <c r="F26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27">
+        <v>2.46</v>
+      </c>
+      <c r="F27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28">
+        <v>2.4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29">
+        <v>3.75</v>
+      </c>
+      <c r="F29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30">
+        <v>2.86</v>
+      </c>
+      <c r="F30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31">
+        <v>3.07</v>
+      </c>
+      <c r="F31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32">
+        <v>1.01</v>
+      </c>
+      <c r="F32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33">
+        <v>3.13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34">
+        <v>3.12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35">
+        <v>0.89</v>
+      </c>
+      <c r="F35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36">
+        <v>2.61</v>
+      </c>
+      <c r="F36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37">
+        <v>1.6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38">
+        <v>1.44</v>
+      </c>
+      <c r="F38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39">
+        <v>2.5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40">
+        <v>1.06</v>
+      </c>
+      <c r="F40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41">
+        <v>0.93</v>
+      </c>
+      <c r="F41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42">
+        <v>0.26</v>
+      </c>
+      <c r="F42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43">
+        <v>0.64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44">
+        <v>1.11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45">
+        <v>3.87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46">
+        <v>3.51</v>
+      </c>
+      <c r="F46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47">
+        <v>2.47</v>
+      </c>
+      <c r="F47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48">
+        <v>3.03</v>
+      </c>
+      <c r="F48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49">
+        <v>2.54</v>
+      </c>
+      <c r="F49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E50">
+        <v>3.37</v>
+      </c>
+      <c r="F50" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51">
+        <v>0.27</v>
+      </c>
+      <c r="F51" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52">
+        <v>3.97</v>
+      </c>
+      <c r="F52" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53">
+        <v>4.33</v>
+      </c>
+      <c r="F53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54">
+        <v>1.39</v>
+      </c>
+      <c r="F54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55">
+        <v>1.41</v>
+      </c>
+      <c r="F55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56">
+        <v>0.38</v>
+      </c>
+      <c r="F56" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57">
+        <v>1.14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" t="s">
+        <v>143</v>
+      </c>
+      <c r="E58">
+        <v>4.49</v>
+      </c>
+      <c r="F58" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59">
+        <v>3.47</v>
+      </c>
+      <c r="F59" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60">
+        <v>2.18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E61">
+        <v>1.59</v>
+      </c>
+      <c r="F61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62">
+        <v>3.03</v>
+      </c>
+      <c r="F62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63">
+        <v>2.64</v>
+      </c>
+      <c r="F63" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>103</v>
+      </c>
+      <c r="D64" t="s">
+        <v>145</v>
+      </c>
+      <c r="E64">
+        <v>3.95</v>
+      </c>
+      <c r="F64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>103</v>
+      </c>
+      <c r="D65" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65">
+        <v>1.36</v>
+      </c>
+      <c r="F65" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>103</v>
+      </c>
+      <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66">
+        <v>3.39</v>
+      </c>
+      <c r="F66" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67">
+        <v>4.44</v>
+      </c>
+      <c r="F67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F68" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
+        <v>99</v>
+      </c>
+      <c r="D69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69">
+        <v>0.33</v>
+      </c>
+      <c r="F69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" t="s">
+        <v>109</v>
+      </c>
+      <c r="E70">
+        <v>4.04</v>
+      </c>
+      <c r="F70" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" t="s">
+        <v>147</v>
+      </c>
+      <c r="E71">
+        <v>4.49</v>
+      </c>
+      <c r="F71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" t="s">
+        <v>141</v>
+      </c>
+      <c r="E72">
+        <v>2.15</v>
+      </c>
+      <c r="F72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" t="s">
+        <v>148</v>
+      </c>
+      <c r="E73">
+        <v>2.15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74">
+        <v>3.82</v>
+      </c>
+      <c r="F74" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" t="s">
+        <v>149</v>
+      </c>
+      <c r="E75">
+        <v>4.12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76">
+        <v>1.78</v>
+      </c>
+      <c r="F76" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>99</v>
+      </c>
+      <c r="D77" t="s">
+        <v>110</v>
+      </c>
+      <c r="E77">
+        <v>4.24</v>
+      </c>
+      <c r="F77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>135</v>
+      </c>
+      <c r="E78">
+        <v>3.16</v>
+      </c>
+      <c r="F78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79">
+        <v>3.6</v>
+      </c>
+      <c r="F79" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80">
+        <v>2.86</v>
+      </c>
+      <c r="F80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+      <c r="C81" t="s">
+        <v>102</v>
+      </c>
+      <c r="D81" t="s">
+        <v>120</v>
+      </c>
+      <c r="E81">
+        <v>1.15</v>
+      </c>
+      <c r="F81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82">
+        <v>0.99</v>
+      </c>
+      <c r="F82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83">
+        <v>0.3</v>
+      </c>
+      <c r="F83" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84">
+        <v>0.33</v>
+      </c>
+      <c r="F84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85">
+        <v>0.91</v>
+      </c>
+      <c r="F85" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" t="s">
+        <v>99</v>
+      </c>
+      <c r="D86" t="s">
+        <v>109</v>
+      </c>
+      <c r="E86">
+        <v>4.19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" t="s">
+        <v>143</v>
+      </c>
+      <c r="E87">
+        <v>1.01</v>
+      </c>
+      <c r="F87" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" t="s">
+        <v>134</v>
+      </c>
+      <c r="E88">
+        <v>1.1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" t="s">
+        <v>107</v>
+      </c>
+      <c r="D89" t="s">
+        <v>134</v>
+      </c>
+      <c r="E89">
+        <v>2.39</v>
+      </c>
+      <c r="F89" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" t="s">
+        <v>103</v>
+      </c>
+      <c r="D90" t="s">
+        <v>151</v>
+      </c>
+      <c r="E90">
+        <v>2.38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" t="s">
+        <v>101</v>
+      </c>
+      <c r="D91" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91">
+        <v>0.24</v>
+      </c>
+      <c r="F91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>96</v>
+      </c>
+      <c r="C92" t="s">
+        <v>103</v>
+      </c>
+      <c r="D92" t="s">
+        <v>130</v>
+      </c>
+      <c r="E92">
+        <v>0.73</v>
+      </c>
+      <c r="F92" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93" t="s">
+        <v>117</v>
+      </c>
+      <c r="E93">
+        <v>2.16</v>
+      </c>
+      <c r="F93" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
